--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2010-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2010-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{30F12E06-7A03-462C-B575-8A4210EFEEB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA167B91-AC7E-45A4-999E-E4366B2BEF0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{6919F0BD-48E4-45FA-98A8-F8301F9853F4}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{4602347E-F0BE-40F3-A578-E8AA361561FD}"/>
   </bookViews>
   <sheets>
     <sheet name="2010-dividend-20260215_1_2" sheetId="2" r:id="rId1"/>
@@ -1634,29 +1634,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652D65AB-B47F-4136-BA89-FC8C0C519424}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2687AB55-8903-417D-BC87-A01E92A8D337}">
   <dimension ref="A1:X58"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.75" customWidth="1"/>
-    <col min="3" max="3" width="9.75" customWidth="1"/>
-    <col min="4" max="4" width="6.25" customWidth="1"/>
-    <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="7" width="6.25" customWidth="1"/>
-    <col min="8" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="6.25" customWidth="1"/>
-    <col min="11" max="13" width="6" customWidth="1"/>
-    <col min="14" max="15" width="6.25" customWidth="1"/>
-    <col min="16" max="18" width="6" customWidth="1"/>
-    <col min="19" max="19" width="6.25" customWidth="1"/>
-    <col min="20" max="20" width="6" customWidth="1"/>
-    <col min="21" max="21" width="6.25" customWidth="1"/>
-    <col min="22" max="22" width="6" customWidth="1"/>
-    <col min="23" max="23" width="6.25" customWidth="1"/>
-    <col min="24" max="24" width="6.875" customWidth="1"/>
+    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="5.77734375" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1690,7 +1689,7 @@
       <c r="W1" s="31"/>
       <c r="X1" s="23"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1726,7 +1725,7 @@
       <c r="W2" s="33"/>
       <c r="X2" s="34"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1778,7 +1777,7 @@
       </c>
       <c r="X3" s="37"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1846,7 +1845,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="38">
         <v>2024</v>
       </c>
@@ -1918,7 +1917,7 @@
         <v>7.67</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="40">
         <v>2023</v>
       </c>
@@ -1990,7 +1989,7 @@
         <v>5.95</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2022</v>
       </c>
@@ -2062,7 +2061,7 @@
         <v>3.83</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="40">
         <v>2021</v>
       </c>
@@ -2134,7 +2133,7 @@
         <v>9.32</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="38">
         <v>2020</v>
       </c>
@@ -2206,7 +2205,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="40">
         <v>2019</v>
       </c>
@@ -2278,7 +2277,7 @@
         <v>3.72</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="38">
         <v>2018</v>
       </c>
@@ -2350,7 +2349,7 @@
         <v>5.63</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="40">
         <v>2017</v>
       </c>
@@ -2422,7 +2421,7 @@
         <v>5.0199999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2016</v>
       </c>
@@ -2494,7 +2493,7 @@
         <v>6.42</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="40">
         <v>2015</v>
       </c>
@@ -2566,7 +2565,7 @@
         <v>5.9</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="38">
         <v>2014</v>
       </c>
@@ -2638,7 +2637,7 @@
         <v>6.25</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="40">
         <v>2013</v>
       </c>
@@ -2710,7 +2709,7 @@
         <v>10.8</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="38">
         <v>2012</v>
       </c>
@@ -2782,7 +2781,7 @@
         <v>4.6500000000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="42">
         <v>2011</v>
       </c>
@@ -2854,7 +2853,7 @@
         <v>7.44</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="44"/>
       <c r="B19" s="45"/>
       <c r="C19" s="19" t="s">
@@ -2882,7 +2881,7 @@
       <c r="W19" s="51"/>
       <c r="X19" s="47"/>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="52">
         <v>2010</v>
       </c>
@@ -2954,7 +2953,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="54"/>
       <c r="B21" s="55"/>
       <c r="C21" s="21" t="s">
@@ -2982,7 +2981,7 @@
       <c r="W21" s="63"/>
       <c r="X21" s="57"/>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="40">
         <v>2009</v>
       </c>
@@ -3054,7 +3053,7 @@
         <v>4.76</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="52">
         <v>2008</v>
       </c>
@@ -3126,7 +3125,7 @@
         <v>5.81</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="54"/>
       <c r="B24" s="55"/>
       <c r="C24" s="21" t="s">
@@ -3154,7 +3153,7 @@
       <c r="W24" s="63"/>
       <c r="X24" s="57"/>
     </row>
-    <row r="25" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="42">
         <v>2007</v>
       </c>
@@ -3226,7 +3225,7 @@
         <v>9.2100000000000009</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="44"/>
       <c r="B26" s="45"/>
       <c r="C26" s="19" t="s">
@@ -3254,7 +3253,7 @@
       <c r="W26" s="51"/>
       <c r="X26" s="47"/>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="52">
         <v>2006</v>
       </c>
@@ -3326,7 +3325,7 @@
         <v>9.82</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="54"/>
       <c r="B28" s="55"/>
       <c r="C28" s="21" t="s">
@@ -3354,7 +3353,7 @@
       <c r="W28" s="63"/>
       <c r="X28" s="57"/>
     </row>
-    <row r="29" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="42">
         <v>2005</v>
       </c>
@@ -3426,7 +3425,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="44"/>
       <c r="B30" s="45"/>
       <c r="C30" s="19" t="s">
@@ -3454,7 +3453,7 @@
       <c r="W30" s="51"/>
       <c r="X30" s="47"/>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="52">
         <v>2004</v>
       </c>
@@ -3526,7 +3525,7 @@
         <v>17.399999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="54"/>
       <c r="B32" s="55"/>
       <c r="C32" s="21" t="s">
@@ -3554,7 +3553,7 @@
       <c r="W32" s="63"/>
       <c r="X32" s="57"/>
     </row>
-    <row r="33" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="42">
         <v>2003</v>
       </c>
@@ -3626,7 +3625,7 @@
         <v>9.09</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="44"/>
       <c r="B34" s="45"/>
       <c r="C34" s="19" t="s">
@@ -3654,7 +3653,7 @@
       <c r="W34" s="51"/>
       <c r="X34" s="47"/>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>2002</v>
       </c>
@@ -3726,7 +3725,7 @@
         <v>11.6</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="40">
         <v>2001</v>
       </c>
@@ -3798,7 +3797,7 @@
         <v>14.7</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>2000</v>
       </c>
@@ -3870,7 +3869,7 @@
         <v>11.7</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="40">
         <v>1999</v>
       </c>
@@ -3942,7 +3941,7 @@
         <v>12.9</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="52">
         <v>1998</v>
       </c>
@@ -4014,7 +4013,7 @@
         <v>4.51</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="54"/>
       <c r="B40" s="55"/>
       <c r="C40" s="21" t="s">
@@ -4042,7 +4041,7 @@
       <c r="W40" s="63"/>
       <c r="X40" s="57"/>
     </row>
-    <row r="41" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="40">
         <v>1997</v>
       </c>
@@ -4114,7 +4113,7 @@
         <v>6.31</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="52">
         <v>1996</v>
       </c>
@@ -4186,7 +4185,7 @@
         <v>7.25</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="54"/>
       <c r="B43" s="55"/>
       <c r="C43" s="21" t="s">
@@ -4214,7 +4213,7 @@
       <c r="W43" s="63"/>
       <c r="X43" s="57"/>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="42">
         <v>1995</v>
       </c>
@@ -4286,7 +4285,7 @@
         <v>5.24</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="44"/>
       <c r="B45" s="45"/>
       <c r="C45" s="19" t="s">
@@ -4314,7 +4313,7 @@
       <c r="W45" s="51"/>
       <c r="X45" s="47"/>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="52">
         <v>1994</v>
       </c>
@@ -4386,7 +4385,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="54"/>
       <c r="B47" s="55"/>
       <c r="C47" s="21" t="s">
@@ -4414,7 +4413,7 @@
       <c r="W47" s="63"/>
       <c r="X47" s="57"/>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="40">
         <v>1993</v>
       </c>
@@ -4486,7 +4485,7 @@
         <v>2.75</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>1992</v>
       </c>
@@ -4558,7 +4557,7 @@
         <v>3.85</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="42">
         <v>1991</v>
       </c>
@@ -4630,7 +4629,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="44"/>
       <c r="B51" s="45"/>
       <c r="C51" s="19" t="s">
@@ -4658,7 +4657,7 @@
       <c r="W51" s="51"/>
       <c r="X51" s="47"/>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="38">
         <v>1990</v>
       </c>
@@ -4730,7 +4729,7 @@
         <v>3.92</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="40">
         <v>1989</v>
       </c>
@@ -4802,7 +4801,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="38">
         <v>1988</v>
       </c>
@@ -4874,7 +4873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="40">
         <v>1987</v>
       </c>
@@ -4946,7 +4945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="38">
         <v>1986</v>
       </c>
@@ -5018,7 +5017,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="40">
         <v>1984</v>
       </c>
@@ -5090,7 +5089,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A58" s="38" t="s">
         <v>77</v>
       </c>
